--- a/diurenmw/Excels/ArmorObj_防具类型表.xlsx
+++ b/diurenmw/Excels/ArmorObj_防具类型表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="500"/>
+    <workbookView windowHeight="17655" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
   <si>
     <t>int</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>effect4</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>stackMax</t>
   </si>
   <si>
     <t>ID</t>
@@ -467,6 +473,12 @@
       </rPr>
       <t>描述</t>
     </r>
+  </si>
+  <si>
+    <t>图标资源id</t>
+  </si>
+  <si>
+    <t>堆叠数量上限</t>
   </si>
   <si>
     <t>普通布甲头盔</t>
@@ -550,6 +562,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -568,13 +587,6 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1009,18 +1021,18 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1144,7 +1156,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -1182,6 +1194,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1715,7 +1728,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="7.46666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.6814814814815" style="1" customWidth="1"/>
@@ -1730,7 +1743,7 @@
     <col min="11" max="13" width="11.6814814814815" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:13">
+    <row r="1" ht="18.75" customHeight="1" spans="1:15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1770,8 +1783,14 @@
       <c r="M1" s="6" t="s">
         <v>1</v>
       </c>
+      <c r="N1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:13">
+    <row r="2" ht="18.75" customHeight="1" spans="1:15">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -1811,46 +1830,58 @@
       <c r="M2" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="N2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" ht="82.5" customHeight="1" spans="1:13">
+    <row r="3" ht="82.5" customHeight="1" spans="1:15">
       <c r="A3" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:9">
@@ -1861,12 +1892,12 @@
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:9">
+    <row r="5" ht="18.75" customHeight="1" spans="1:15">
       <c r="A5">
         <v>10001</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
@@ -1884,10 +1915,16 @@
         <v>16</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="N5">
+        <v>95598</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:9">
@@ -1900,12 +1937,12 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:9">
+    <row r="7" ht="18.75" customHeight="1" spans="1:15">
       <c r="A7">
         <v>20001</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4">
         <v>2</v>
@@ -1923,18 +1960,24 @@
         <v>100</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="N7">
+        <v>336185</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:13">
+    <row r="8" ht="18.75" customHeight="1" spans="1:15">
       <c r="A8">
         <v>20002</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4">
         <v>2</v>
@@ -1952,22 +1995,28 @@
         <v>1000</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="N8">
+        <v>336185</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:9">
@@ -1980,12 +2029,12 @@
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:9">
+    <row r="10" ht="18.75" customHeight="1" spans="1:15">
       <c r="A10">
         <v>30001</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3">
         <v>3</v>
@@ -2003,10 +2052,16 @@
         <v>10</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>39</v>
+        <v>43</v>
+      </c>
+      <c r="N10">
+        <v>314966</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:9">
@@ -2019,12 +2074,12 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:9">
+    <row r="12" ht="18.75" customHeight="1" spans="1:15">
       <c r="A12">
         <v>40001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C12" s="3">
         <v>4</v>
@@ -2042,10 +2097,16 @@
         <v>10</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="N12">
+        <v>95590</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:9">

--- a/diurenmw/Excels/ArmorObj_防具类型表.xlsx
+++ b/diurenmw/Excels/ArmorObj_防具类型表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="500"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="73">
   <si>
     <t>int</t>
   </si>
@@ -87,27 +87,21 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">防具部位：
+</t>
+    </r>
+    <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">防具部位：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
         <charset val="1"/>
       </rPr>
       <t>1.</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
         <charset val="134"/>
@@ -117,16 +111,16 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="微软雅黑"/>
         <charset val="1"/>
       </rPr>
       <t>2.</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
         <charset val="134"/>
@@ -136,16 +130,16 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="微软雅黑"/>
         <charset val="1"/>
       </rPr>
       <t>3.</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
         <charset val="134"/>
@@ -155,24 +149,13 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="微软雅黑"/>
         <charset val="1"/>
       </rPr>
       <t>4.</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>鞋子</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -180,6 +163,11 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
+      <t>鞋子</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">防具种类：
 </t>
     </r>
@@ -187,7 +175,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="微软雅黑"/>
         <charset val="1"/>
       </rPr>
       <t>1.</t>
@@ -206,7 +194,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="微软雅黑"/>
         <charset val="1"/>
       </rPr>
       <t>2.</t>
@@ -225,7 +213,7 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="微软雅黑"/>
         <charset val="1"/>
       </rPr>
       <t>3.</t>
@@ -241,138 +229,33 @@
     </r>
   </si>
   <si>
+    <t>品级：
+1.普通
+2.高级
+3.稀有
+4.史诗</t>
+  </si>
+  <si>
+    <t>防御力</t>
+  </si>
+  <si>
+    <t>体力</t>
+  </si>
+  <si>
+    <t>力量范围</t>
+  </si>
+  <si>
+    <t>智力范围</t>
+  </si>
+  <si>
+    <r>
+      <t>效果</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">品级：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">普通
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">高级
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">稀有
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">传说
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>史诗</t>
-    </r>
-  </si>
-  <si>
-    <t>防御力</t>
-  </si>
-  <si>
-    <t>体力</t>
-  </si>
-  <si>
-    <t>力量范围</t>
-  </si>
-  <si>
-    <t>智力范围</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>效果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
         <charset val="1"/>
       </rPr>
       <t>1</t>
@@ -389,19 +272,13 @@
   </si>
   <si>
     <r>
+      <t>效果</t>
+    </r>
+    <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>效果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
         <charset val="1"/>
       </rPr>
       <t>2</t>
@@ -418,19 +295,13 @@
   </si>
   <si>
     <r>
+      <t>效果</t>
+    </r>
+    <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>效果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
         <charset val="1"/>
       </rPr>
       <t>3</t>
@@ -447,19 +318,13 @@
   </si>
   <si>
     <r>
+      <t>效果</t>
+    </r>
+    <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>效果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
         <charset val="1"/>
       </rPr>
       <t>4</t>
@@ -484,46 +349,124 @@
     <t>普通布甲头盔</t>
   </si>
   <si>
-    <t>12|20</t>
-  </si>
-  <si>
-    <t>50|100</t>
+    <t>2|3</t>
+  </si>
+  <si>
+    <t>1|2</t>
+  </si>
+  <si>
+    <t>生命值增加27</t>
+  </si>
+  <si>
+    <t>剑气纵横头盔</t>
+  </si>
+  <si>
+    <t>55|70</t>
+  </si>
+  <si>
+    <t>41|59</t>
+  </si>
+  <si>
+    <t>生命值增加1200</t>
+  </si>
+  <si>
+    <t>剑气波消耗增加50％</t>
+  </si>
+  <si>
+    <t>剑气波伤害增加50％</t>
+  </si>
+  <si>
+    <t>剑气波大小增加30％</t>
   </si>
   <si>
     <t>锁子甲</t>
   </si>
   <si>
-    <t>100|150</t>
-  </si>
-  <si>
-    <t>20|50</t>
-  </si>
-  <si>
-    <t>银鳞胸甲</t>
-  </si>
-  <si>
-    <t>600|800</t>
-  </si>
-  <si>
-    <t>100|120</t>
+    <t>3|5</t>
+  </si>
+  <si>
+    <t>生命值增加58</t>
+  </si>
+  <si>
+    <t>剑气纵横胸甲</t>
+  </si>
+  <si>
+    <t>90|110</t>
+  </si>
+  <si>
+    <t>70|93</t>
+  </si>
+  <si>
+    <t>生命值增加2000</t>
+  </si>
+  <si>
+    <t>技能伤增加10％</t>
+  </si>
+  <si>
+    <t>剑气波伤害增加10％</t>
+  </si>
+  <si>
+    <t>剑气波释放的剑气数量+2</t>
   </si>
   <si>
     <t>普通布甲下装</t>
   </si>
   <si>
-    <t>13|22</t>
-  </si>
-  <si>
-    <t>77|98</t>
+    <t>2|4</t>
+  </si>
+  <si>
+    <t>1|3</t>
+  </si>
+  <si>
+    <t>生命值增加43</t>
+  </si>
+  <si>
+    <t>剑刃无双护腿</t>
+  </si>
+  <si>
+    <t>77|90</t>
+  </si>
+  <si>
+    <t>59|78</t>
+  </si>
+  <si>
+    <t>生命值增加1550</t>
+  </si>
+  <si>
+    <t>暴伤增加15％</t>
+  </si>
+  <si>
+    <t>拔刀斩CD+1s</t>
+  </si>
+  <si>
+    <t>拔刀斩增加收刀动作，追加60％伤害</t>
   </si>
   <si>
     <t>普通重甲鞋子</t>
   </si>
   <si>
-    <t>5|8</t>
-  </si>
-  <si>
-    <t>16|21</t>
+    <t>生命值增加15</t>
+  </si>
+  <si>
+    <t>剑刃无双战靴</t>
+  </si>
+  <si>
+    <t>43|50</t>
+  </si>
+  <si>
+    <t>21|44</t>
+  </si>
+  <si>
+    <t>生命值增加860</t>
+  </si>
+  <si>
+    <t>移动速度增加20％</t>
+  </si>
+  <si>
+    <t>拔刀斩范围增加50％</t>
+  </si>
+  <si>
+    <t>拔刀斩伤害增加20％</t>
   </si>
 </sst>
 </file>
@@ -546,27 +489,20 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -587,6 +523,13 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1021,18 +964,18 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1156,45 +1099,50 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1728,476 +1676,617 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultColWidth="7.46666666666667" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.6814814814815" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.6296296296296" style="2" customWidth="1"/>
-    <col min="3" max="3" width="37.0962962962963" style="3" customWidth="1"/>
+    <col min="3" max="3" width="37.0962962962963" style="2" customWidth="1"/>
     <col min="4" max="4" width="28" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.0518518518519" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.4296296296296" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.6814814814815" style="3" customWidth="1"/>
-    <col min="8" max="9" width="11.6814814814815" style="4" customWidth="1"/>
-    <col min="10" max="10" width="11.8" style="3" customWidth="1"/>
-    <col min="11" max="13" width="11.6814814814815" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11.6814814814815" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.6814814814815" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.8" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15" style="2" customWidth="1"/>
+    <col min="13" max="13" width="26.2222222222222" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="7.46666666666667" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" ht="82.5" customHeight="1" spans="1:15">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="15" t="s">
+      <c r="O3" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A5">
+      <c r="A5" s="3">
         <v>10001</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>3</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>1</v>
       </c>
-      <c r="F5" s="12">
-        <v>15</v>
-      </c>
-      <c r="G5" s="12">
+      <c r="F5" s="11">
+        <v>9</v>
+      </c>
+      <c r="G5" s="11">
+        <v>7</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="3">
+        <v>95598</v>
+      </c>
+      <c r="O5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A6" s="3">
+        <v>10002</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="10">
+        <v>4</v>
+      </c>
+      <c r="F6" s="11">
+        <v>400</v>
+      </c>
+      <c r="G6" s="11">
+        <v>160</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" s="3">
+        <v>68420</v>
+      </c>
+      <c r="O6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" spans="1:9">
+      <c r="A7" s="3"/>
+      <c r="B7" s="5"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A8" s="3">
+        <v>20001</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="11">
+        <v>22</v>
+      </c>
+      <c r="G8" s="11">
+        <v>23</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" s="3">
+        <v>336185</v>
+      </c>
+      <c r="O8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A9" s="3">
+        <v>20002</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4">
+        <v>4</v>
+      </c>
+      <c r="F9" s="11">
+        <v>800</v>
+      </c>
+      <c r="G9" s="11">
+        <v>350</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="3">
+        <v>336533</v>
+      </c>
+      <c r="O9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" spans="1:9">
+      <c r="A10" s="3"/>
+      <c r="B10" s="5"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A11" s="3">
+        <v>30001</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11">
         <v>16</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="12" t="s">
+      <c r="G11" s="11">
+        <v>18</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="3">
+        <v>314966</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A12" s="12">
+        <v>30002</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12">
+        <v>4</v>
+      </c>
+      <c r="F12" s="6">
+        <v>580</v>
+      </c>
+      <c r="G12" s="6">
+        <v>270</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12" s="3">
+        <v>87817</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customHeight="1" spans="1:9">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A14" s="3">
+        <v>40001</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
+        <v>5</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N5">
-        <v>95598</v>
-      </c>
-      <c r="O5">
+      <c r="I14" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A6"/>
-      <c r="B6" s="6"/>
-      <c r="D6"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A7">
-        <v>20001</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2</v>
-      </c>
-      <c r="D7">
+      <c r="J14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N14" s="3">
+        <v>95590</v>
+      </c>
+      <c r="O14" s="3">
         <v>1</v>
       </c>
-      <c r="E7" s="13">
+    </row>
+    <row r="15" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A15" s="4">
+        <v>40002</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="2">
+        <v>4</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4">
+        <v>4</v>
+      </c>
+      <c r="F15" s="5">
+        <v>350</v>
+      </c>
+      <c r="G15" s="2">
+        <v>120</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N15" s="3">
+        <v>26871</v>
+      </c>
+      <c r="O15" s="3">
         <v>1</v>
       </c>
-      <c r="F7" s="12">
-        <v>22</v>
-      </c>
-      <c r="G7" s="12">
-        <v>100</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="N7">
-        <v>336185</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A8">
-        <v>20002</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8" s="13">
-        <v>5</v>
-      </c>
-      <c r="F8" s="12">
-        <v>1600</v>
-      </c>
-      <c r="G8" s="12">
-        <v>1000</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8">
-        <v>336185</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A9"/>
-      <c r="B9" s="6"/>
-      <c r="D9"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-    </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A10">
-        <v>30001</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="3">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="12">
-        <v>16</v>
-      </c>
-      <c r="G10" s="12">
-        <v>10</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="N10">
-        <v>314966</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A12">
-        <v>40001</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="3">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12">
-        <v>95590</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="5"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="5"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="5"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="5"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="5"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:9">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="5"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" ht="18.75" customHeight="1" spans="1:9">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+    </row>
+    <row r="24" ht="18.75" customHeight="1" spans="1:9">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="5"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
